--- a/notebooks/data/reports/freshness_audit_scoring.xlsx
+++ b/notebooks/data/reports/freshness_audit_scoring.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1351"/>
+  <dimension ref="A1:H1381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35359,17 +35359,17 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>-0.2513801</v>
+        <v>8.053368000000001</v>
       </c>
       <c r="D1112" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1112" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1112" t="b">
         <v>0</v>
@@ -35391,17 +35391,17 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1113" t="n">
-        <v>0.2509955</v>
+        <v>10.68561</v>
       </c>
       <c r="D1113" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1113" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1113" t="b">
         <v>0</v>
@@ -35423,17 +35423,17 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1114" t="n">
-        <v>-0.39715</v>
+        <v>2.438341</v>
       </c>
       <c r="D1114" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E1114" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F1114" t="b">
         <v>0</v>
@@ -35455,17 +35455,17 @@
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>-1.267722</v>
+        <v>7.4384</v>
       </c>
       <c r="D1115" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1115" t="b">
         <v>0</v>
@@ -35487,17 +35487,17 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1116" t="n">
-        <v>-0.446218</v>
+        <v>13.24288</v>
       </c>
       <c r="D1116" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1116" t="b">
         <v>0</v>
@@ -35519,17 +35519,17 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>0.7277751</v>
+        <v>10.99324</v>
       </c>
       <c r="D1117" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1117" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1117" t="b">
         <v>0</v>
@@ -35551,17 +35551,17 @@
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1118" t="n">
-        <v>1.4608299</v>
+        <v>14.87579</v>
       </c>
       <c r="D1118" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1118" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1118" t="b">
         <v>0</v>
@@ -35583,17 +35583,17 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1119" t="n">
-        <v>0.6910553</v>
+        <v>15.05532</v>
       </c>
       <c r="D1119" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1119" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1119" t="b">
         <v>0</v>
@@ -35615,17 +35615,17 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1120" t="n">
-        <v>-0.5597434</v>
+        <v>3.627367</v>
       </c>
       <c r="D1120" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1120" t="b">
         <v>0</v>
@@ -35647,17 +35647,17 @@
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1121" t="n">
-        <v>0.6167412</v>
+        <v>6.895765</v>
       </c>
       <c r="D1121" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1121" t="b">
         <v>0</v>
@@ -35679,17 +35679,17 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1122" t="n">
-        <v>-0.6235716</v>
+        <v>9.080363999999999</v>
       </c>
       <c r="D1122" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E1122" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F1122" t="b">
         <v>0</v>
@@ -35711,17 +35711,17 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>-0.1822626</v>
+        <v>20.06032</v>
       </c>
       <c r="D1123" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1123" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1123" t="b">
         <v>0</v>
@@ -35743,17 +35743,17 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>-0.9650369</v>
+        <v>7.521531</v>
       </c>
       <c r="D1124" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1124" t="b">
         <v>0</v>
@@ -35775,17 +35775,17 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1125" t="n">
-        <v>0.9317736</v>
+        <v>6.80667</v>
       </c>
       <c r="D1125" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1125" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1125" t="b">
         <v>0</v>
@@ -35807,17 +35807,17 @@
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1126" t="n">
-        <v>-0.962274</v>
+        <v>17.11524</v>
       </c>
       <c r="D1126" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1126" t="b">
         <v>0</v>
@@ -35839,17 +35839,17 @@
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>-0.334222099999999</v>
+        <v>12.96359</v>
       </c>
       <c r="D1127" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1127" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1127" t="b">
         <v>0</v>
@@ -35871,17 +35871,17 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>-1.1768036</v>
+        <v>10.18443</v>
       </c>
       <c r="D1128" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1128" t="b">
         <v>0</v>
@@ -35903,17 +35903,17 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>-1.6033955</v>
+        <v>18.03271</v>
       </c>
       <c r="D1129" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1129" t="b">
         <v>0</v>
@@ -35935,17 +35935,17 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>-0.07766969999999999</v>
+        <v>11.24154</v>
       </c>
       <c r="D1130" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1130" t="b">
         <v>0</v>
@@ -35967,17 +35967,17 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>-1.15386449999999</v>
+        <v>14.32171</v>
       </c>
       <c r="D1131" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1131" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1131" t="b">
         <v>0</v>
@@ -35999,17 +35999,17 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>-1.6197013</v>
+        <v>9.802580000000001</v>
       </c>
       <c r="D1132" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1132" t="b">
         <v>0</v>
@@ -36031,17 +36031,17 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>-0.2634275</v>
+        <v>10.18564</v>
       </c>
       <c r="D1133" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1133" t="b">
         <v>0</v>
@@ -36063,17 +36063,17 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>-0.5057749</v>
+        <v>12.21068</v>
       </c>
       <c r="D1134" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1134" t="b">
         <v>0</v>
@@ -36095,17 +36095,17 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>-0.5835849</v>
+        <v>13.30168</v>
       </c>
       <c r="D1135" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1135" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1135" t="b">
         <v>0</v>
@@ -36127,17 +36127,17 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>-0.7133592</v>
+        <v>8.307817</v>
       </c>
       <c r="D1136" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1136" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1136" t="b">
         <v>0</v>
@@ -36159,27 +36159,27 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>-0.2085757</v>
+        <v>5.680528</v>
       </c>
       <c r="D1137" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="E1137" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F1137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1137" t="b">
         <v>0</v>
       </c>
       <c r="H1137" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -36191,17 +36191,17 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>-0.371533</v>
+        <v>6.692461</v>
       </c>
       <c r="D1138" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1138" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1138" t="b">
         <v>0</v>
@@ -36223,17 +36223,17 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>0.9505638</v>
+        <v>15.07057</v>
       </c>
       <c r="D1139" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1139" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1139" t="b">
         <v>0</v>
@@ -36255,17 +36255,17 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>0.9617896</v>
+        <v>12.51984</v>
       </c>
       <c r="D1140" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1140" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1140" t="b">
         <v>0</v>
@@ -36287,17 +36287,17 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>rule_of_law</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>-2.20427409999999</v>
+        <v>5.545743</v>
       </c>
       <c r="D1141" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E1141" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1141" t="b">
         <v>0</v>
@@ -36319,11 +36319,11 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>5453.43428098629</v>
+        <v>-0.2513801</v>
       </c>
       <c r="D1142" t="n">
         <v>2024</v>
@@ -36351,11 +36351,11 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>6354.61756416295</v>
+        <v>0.2509955</v>
       </c>
       <c r="D1143" t="n">
         <v>2024</v>
@@ -36383,11 +36383,11 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>464560.075958108</v>
+        <v>-0.39715</v>
       </c>
       <c r="D1144" t="n">
         <v>2024</v>
@@ -36415,11 +36415,11 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>364.447369618833</v>
+        <v>-1.267722</v>
       </c>
       <c r="D1145" t="n">
         <v>2024</v>
@@ -36447,11 +36447,11 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>6941.17408045006</v>
+        <v>-0.446218</v>
       </c>
       <c r="D1146" t="n">
         <v>2024</v>
@@ -36479,11 +36479,11 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>1171.81830089887</v>
+        <v>0.7277751</v>
       </c>
       <c r="D1147" t="n">
         <v>2024</v>
@@ -36511,11 +36511,11 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>39712.7546032744</v>
+        <v>1.4608299</v>
       </c>
       <c r="D1148" t="n">
         <v>2024</v>
@@ -36543,11 +36543,11 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>11912.6095617298</v>
+        <v>0.6910553</v>
       </c>
       <c r="D1149" t="n">
         <v>2024</v>
@@ -36575,11 +36575,11 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>1126.20714719974</v>
+        <v>-0.5597434</v>
       </c>
       <c r="D1150" t="n">
         <v>2024</v>
@@ -36607,11 +36607,11 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>1999.84015314109</v>
+        <v>0.6167412</v>
       </c>
       <c r="D1151" t="n">
         <v>2024</v>
@@ -36639,11 +36639,11 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>192.535681260732</v>
+        <v>-0.6235716</v>
       </c>
       <c r="D1152" t="n">
         <v>2024</v>
@@ -36671,11 +36671,11 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>180.878555232759</v>
+        <v>-0.1822626</v>
       </c>
       <c r="D1153" t="n">
         <v>2024</v>
@@ -36703,11 +36703,11 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>490.861062498601</v>
+        <v>-0.9650369</v>
       </c>
       <c r="D1154" t="n">
         <v>2024</v>
@@ -36735,11 +36735,11 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>29986.3824811398</v>
+        <v>0.9317736</v>
       </c>
       <c r="D1155" t="n">
         <v>2024</v>
@@ -36767,11 +36767,11 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>109.147061621475</v>
+        <v>-0.962274</v>
       </c>
       <c r="D1156" t="n">
         <v>2024</v>
@@ -36799,11 +36799,11 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>175.673545609545</v>
+        <v>-0.334222099999999</v>
       </c>
       <c r="D1157" t="n">
         <v>2024</v>
@@ -36831,11 +36831,11 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>148.812506679705</v>
+        <v>-1.1768036</v>
       </c>
       <c r="D1158" t="n">
         <v>2024</v>
@@ -36863,11 +36863,11 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>7.72984152890489</v>
+        <v>-1.6033955</v>
       </c>
       <c r="D1159" t="n">
         <v>2024</v>
@@ -36895,11 +36895,11 @@
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>191.957170656969</v>
+        <v>-0.07766969999999999</v>
       </c>
       <c r="D1160" t="n">
         <v>2024</v>
@@ -36927,11 +36927,11 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>531.655697865752</v>
+        <v>-1.15386449999999</v>
       </c>
       <c r="D1161" t="n">
         <v>2024</v>
@@ -36959,11 +36959,11 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>93.9830599149236</v>
+        <v>-1.6197013</v>
       </c>
       <c r="D1162" t="n">
         <v>2024</v>
@@ -36991,11 +36991,11 @@
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>2234.48741988012</v>
+        <v>-0.2634275</v>
       </c>
       <c r="D1163" t="n">
         <v>2024</v>
@@ -37023,11 +37023,11 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>826.790743824685</v>
+        <v>-0.5057749</v>
       </c>
       <c r="D1164" t="n">
         <v>2024</v>
@@ -37055,11 +37055,11 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>775.275131029723</v>
+        <v>-0.5835849</v>
       </c>
       <c r="D1165" t="n">
         <v>2024</v>
@@ -37087,11 +37087,11 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>191.221693627821</v>
+        <v>-0.7133592</v>
       </c>
       <c r="D1166" t="n">
         <v>2024</v>
@@ -37119,11 +37119,11 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>2060.11370818891</v>
+        <v>-0.2085757</v>
       </c>
       <c r="D1167" t="n">
         <v>2024</v>
@@ -37151,11 +37151,11 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>480.146280181798</v>
+        <v>-0.371533</v>
       </c>
       <c r="D1168" t="n">
         <v>2024</v>
@@ -37183,11 +37183,11 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>4640.65897593684</v>
+        <v>0.9505638</v>
       </c>
       <c r="D1169" t="n">
         <v>2024</v>
@@ -37215,11 +37215,11 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>196554.134852003</v>
+        <v>0.9617896</v>
       </c>
       <c r="D1170" t="n">
         <v>2024</v>
@@ -37247,11 +37247,11 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>rule_of_law</t>
         </is>
       </c>
       <c r="C1171" t="n">
-        <v>246.677206628298</v>
+        <v>-2.20427409999999</v>
       </c>
       <c r="D1171" t="n">
         <v>2024</v>
@@ -37279,17 +37279,17 @@
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>8.35147499068672</v>
+        <v>5453.43428098629</v>
       </c>
       <c r="D1172" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1172" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1172" t="b">
         <v>0</v>
@@ -37311,21 +37311,27 @@
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1173" t="inlineStr"/>
-      <c r="D1173" t="inlineStr"/>
-      <c r="E1173" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>6354.61756416295</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>2</v>
+      </c>
       <c r="F1173" t="b">
         <v>0</v>
       </c>
       <c r="G1173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1173" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37337,21 +37343,27 @@
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1174" t="inlineStr"/>
-      <c r="D1174" t="inlineStr"/>
-      <c r="E1174" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>464560.075958108</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>2</v>
+      </c>
       <c r="F1174" t="b">
         <v>0</v>
       </c>
       <c r="G1174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1174" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37363,21 +37375,27 @@
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1175" t="inlineStr"/>
-      <c r="D1175" t="inlineStr"/>
-      <c r="E1175" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>364.447369618833</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>2</v>
+      </c>
       <c r="F1175" t="b">
         <v>0</v>
       </c>
       <c r="G1175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1175" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37389,11 +37407,11 @@
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>30.1448139796022</v>
+        <v>6941.17408045006</v>
       </c>
       <c r="D1176" t="n">
         <v>2024</v>
@@ -37421,17 +37439,17 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>51.4223097622548</v>
+        <v>1171.81830089887</v>
       </c>
       <c r="D1177" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E1177" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F1177" t="b">
         <v>0</v>
@@ -37453,11 +37471,11 @@
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>150.402111872218</v>
+        <v>39712.7546032744</v>
       </c>
       <c r="D1178" t="n">
         <v>2024</v>
@@ -37485,11 +37503,11 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>79.3329036867525</v>
+        <v>11912.6095617298</v>
       </c>
       <c r="D1179" t="n">
         <v>2024</v>
@@ -37517,11 +37535,11 @@
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>17.3434816885955</v>
+        <v>1126.20714719974</v>
       </c>
       <c r="D1180" t="n">
         <v>2024</v>
@@ -37549,17 +37567,17 @@
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>3.22348803495399</v>
+        <v>1999.84015314109</v>
       </c>
       <c r="D1181" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1181" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1181" t="b">
         <v>0</v>
@@ -37581,21 +37599,27 @@
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1182" t="inlineStr"/>
-      <c r="D1182" t="inlineStr"/>
-      <c r="E1182" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>192.535681260732</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>2</v>
+      </c>
       <c r="F1182" t="b">
         <v>0</v>
       </c>
       <c r="G1182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1182" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37607,21 +37631,27 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1183" t="inlineStr"/>
-      <c r="D1183" t="inlineStr"/>
-      <c r="E1183" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>180.878555232759</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>2</v>
+      </c>
       <c r="F1183" t="b">
         <v>0</v>
       </c>
       <c r="G1183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1183" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37633,27 +37663,27 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>4.25896934432397</v>
+        <v>490.861062498601</v>
       </c>
       <c r="D1184" t="n">
-        <v>2000</v>
+        <v>2024</v>
       </c>
       <c r="E1184" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F1184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1184" t="b">
         <v>0</v>
       </c>
       <c r="H1184" t="inlineStr">
         <is>
-          <t>stale_replaced_by_missing</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37665,11 +37695,11 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>43.6927754362693</v>
+        <v>29986.3824811398</v>
       </c>
       <c r="D1185" t="n">
         <v>2024</v>
@@ -37697,21 +37727,27 @@
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1186" t="inlineStr"/>
-      <c r="D1186" t="inlineStr"/>
-      <c r="E1186" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1186" t="n">
+        <v>109.147061621475</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>2</v>
+      </c>
       <c r="F1186" t="b">
         <v>0</v>
       </c>
       <c r="G1186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1186" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37723,21 +37759,27 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1187" t="inlineStr"/>
-      <c r="D1187" t="inlineStr"/>
-      <c r="E1187" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1187" t="n">
+        <v>175.673545609545</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>2</v>
+      </c>
       <c r="F1187" t="b">
         <v>0</v>
       </c>
       <c r="G1187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1187" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37749,21 +37791,27 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1188" t="inlineStr"/>
-      <c r="D1188" t="inlineStr"/>
-      <c r="E1188" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1188" t="n">
+        <v>148.812506679705</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>2</v>
+      </c>
       <c r="F1188" t="b">
         <v>0</v>
       </c>
       <c r="G1188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1188" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37775,21 +37823,27 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1189" t="inlineStr"/>
-      <c r="D1189" t="inlineStr"/>
-      <c r="E1189" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1189" t="n">
+        <v>7.72984152890489</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>2</v>
+      </c>
       <c r="F1189" t="b">
         <v>0</v>
       </c>
       <c r="G1189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1189" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37801,11 +37855,11 @@
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>56.4593704261673</v>
+        <v>191.957170656969</v>
       </c>
       <c r="D1190" t="n">
         <v>2024</v>
@@ -37833,17 +37887,17 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>32.0669850496152</v>
+        <v>531.655697865752</v>
       </c>
       <c r="D1191" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E1191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1191" t="b">
         <v>0</v>
@@ -37865,21 +37919,27 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1192" t="inlineStr"/>
-      <c r="D1192" t="inlineStr"/>
-      <c r="E1192" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1192" t="n">
+        <v>93.9830599149236</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>2</v>
+      </c>
       <c r="F1192" t="b">
         <v>0</v>
       </c>
       <c r="G1192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1192" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37891,11 +37951,11 @@
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>21.136342099364</v>
+        <v>2234.48741988012</v>
       </c>
       <c r="D1193" t="n">
         <v>2024</v>
@@ -37923,11 +37983,11 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>28.4196149643503</v>
+        <v>826.790743824685</v>
       </c>
       <c r="D1194" t="n">
         <v>2024</v>
@@ -37955,27 +38015,27 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1195" t="n">
-        <v>3.5396346488541</v>
+        <v>775.275131029723</v>
       </c>
       <c r="D1195" t="n">
-        <v>1999</v>
+        <v>2024</v>
       </c>
       <c r="E1195" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F1195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1195" t="b">
         <v>0</v>
       </c>
       <c r="H1195" t="inlineStr">
         <is>
-          <t>stale_replaced_by_missing</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -37987,21 +38047,27 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1196" t="inlineStr"/>
-      <c r="D1196" t="inlineStr"/>
-      <c r="E1196" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1196" t="n">
+        <v>191.221693627821</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>2</v>
+      </c>
       <c r="F1196" t="b">
         <v>0</v>
       </c>
       <c r="G1196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1196" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -38013,21 +38079,27 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
-        </is>
-      </c>
-      <c r="C1197" t="inlineStr"/>
-      <c r="D1197" t="inlineStr"/>
-      <c r="E1197" t="inlineStr"/>
+          <t>secure_internet_servers_per_million</t>
+        </is>
+      </c>
+      <c r="C1197" t="n">
+        <v>2060.11370818891</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>2</v>
+      </c>
       <c r="F1197" t="b">
         <v>0</v>
       </c>
       <c r="G1197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1197" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -38039,27 +38111,27 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1198" t="n">
-        <v>44.0698749158292</v>
+        <v>480.146280181798</v>
       </c>
       <c r="D1198" t="n">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="E1198" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F1198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1198" t="b">
         <v>0</v>
       </c>
       <c r="H1198" t="inlineStr">
         <is>
-          <t>stale_replaced_by_missing</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -38071,27 +38143,27 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1199" t="n">
-        <v>1.38334712502502</v>
+        <v>4640.65897593684</v>
       </c>
       <c r="D1199" t="n">
-        <v>1996</v>
+        <v>2024</v>
       </c>
       <c r="E1199" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F1199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1199" t="b">
         <v>0</v>
       </c>
       <c r="H1199" t="inlineStr">
         <is>
-          <t>stale_replaced_by_missing</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -38103,11 +38175,11 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1200" t="n">
-        <v>216.290842771421</v>
+        <v>196554.134852003</v>
       </c>
       <c r="D1200" t="n">
         <v>2024</v>
@@ -38135,27 +38207,27 @@
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>stock_market_cap_gdp</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="C1201" t="n">
-        <v>4.28404166217623</v>
+        <v>246.677206628298</v>
       </c>
       <c r="D1201" t="n">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="E1201" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F1201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1201" t="b">
         <v>0</v>
       </c>
       <c r="H1201" t="inlineStr">
         <is>
-          <t>stale_replaced_by_missing</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -38167,17 +38239,17 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1202" t="n">
-        <v>27.929760849367</v>
+        <v>8.35147499068672</v>
       </c>
       <c r="D1202" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E1202" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1202" t="b">
         <v>0</v>
@@ -38199,27 +38271,21 @@
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1203" t="n">
-        <v>79.2424586933455</v>
-      </c>
-      <c r="D1203" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1203" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr"/>
+      <c r="D1203" t="inlineStr"/>
+      <c r="E1203" t="inlineStr"/>
       <c r="F1203" t="b">
         <v>0</v>
       </c>
       <c r="G1203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1203" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38231,27 +38297,21 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1204" t="n">
-        <v>108.972446521476</v>
-      </c>
-      <c r="D1204" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1204" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr"/>
+      <c r="D1204" t="inlineStr"/>
+      <c r="E1204" t="inlineStr"/>
       <c r="F1204" t="b">
         <v>0</v>
       </c>
       <c r="G1204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1204" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38263,27 +38323,21 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1205" t="n">
-        <v>46.9778716148403</v>
-      </c>
-      <c r="D1205" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1205" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr"/>
+      <c r="D1205" t="inlineStr"/>
+      <c r="E1205" t="inlineStr"/>
       <c r="F1205" t="b">
         <v>0</v>
       </c>
       <c r="G1205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1205" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38295,11 +38349,11 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1206" t="n">
-        <v>35.5845239385389</v>
+        <v>30.1448139796022</v>
       </c>
       <c r="D1206" t="n">
         <v>2024</v>
@@ -38327,21 +38381,27 @@
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1207" t="inlineStr"/>
-      <c r="D1207" t="inlineStr"/>
-      <c r="E1207" t="inlineStr"/>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1207" t="n">
+        <v>51.4223097622548</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>6</v>
+      </c>
       <c r="F1207" t="b">
         <v>0</v>
       </c>
       <c r="G1207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1207" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -38353,11 +38413,11 @@
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1208" t="n">
-        <v>65.1499212653783</v>
+        <v>150.402111872218</v>
       </c>
       <c r="D1208" t="n">
         <v>2024</v>
@@ -38385,11 +38445,11 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1209" t="n">
-        <v>63.859857248066</v>
+        <v>79.3329036867525</v>
       </c>
       <c r="D1209" t="n">
         <v>2024</v>
@@ -38417,11 +38477,11 @@
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1210" t="n">
-        <v>37.0254687077888</v>
+        <v>17.3434816885955</v>
       </c>
       <c r="D1210" t="n">
         <v>2024</v>
@@ -38449,17 +38509,17 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1211" t="n">
-        <v>71.33101376876169</v>
+        <v>3.22348803495399</v>
       </c>
       <c r="D1211" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E1211" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1211" t="b">
         <v>0</v>
@@ -38481,27 +38541,21 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1212" t="n">
-        <v>124.863238865053</v>
-      </c>
-      <c r="D1212" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1212" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr"/>
+      <c r="D1212" t="inlineStr"/>
+      <c r="E1212" t="inlineStr"/>
       <c r="F1212" t="b">
         <v>0</v>
       </c>
       <c r="G1212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1212" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38513,27 +38567,21 @@
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1213" t="n">
-        <v>51.7835143952326</v>
-      </c>
-      <c r="D1213" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1213" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr"/>
+      <c r="D1213" t="inlineStr"/>
+      <c r="E1213" t="inlineStr"/>
       <c r="F1213" t="b">
         <v>0</v>
       </c>
       <c r="G1213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1213" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38545,27 +38593,27 @@
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1214" t="n">
-        <v>57.2031395531255</v>
+        <v>4.25896934432397</v>
       </c>
       <c r="D1214" t="n">
-        <v>2024</v>
+        <v>2000</v>
       </c>
       <c r="E1214" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="F1214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1214" t="b">
         <v>0</v>
       </c>
       <c r="H1214" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -38577,11 +38625,11 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1215" t="n">
-        <v>69.9502612382631</v>
+        <v>43.6927754362693</v>
       </c>
       <c r="D1215" t="n">
         <v>2024</v>
@@ -38609,27 +38657,21 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1216" t="n">
-        <v>47.344196760267</v>
-      </c>
-      <c r="D1216" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1216" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr"/>
+      <c r="D1216" t="inlineStr"/>
+      <c r="E1216" t="inlineStr"/>
       <c r="F1216" t="b">
         <v>0</v>
       </c>
       <c r="G1216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1216" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38641,27 +38683,21 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1217" t="n">
-        <v>194.350757310172</v>
-      </c>
-      <c r="D1217" t="n">
-        <v>2005</v>
-      </c>
-      <c r="E1217" t="n">
-        <v>21</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr"/>
+      <c r="D1217" t="inlineStr"/>
+      <c r="E1217" t="inlineStr"/>
       <c r="F1217" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1217" t="b">
         <v>1</v>
       </c>
-      <c r="G1217" t="b">
-        <v>0</v>
-      </c>
       <c r="H1217" t="inlineStr">
         <is>
-          <t>stale_replaced_by_missing</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38673,27 +38709,21 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1218" t="n">
-        <v>91.1101585856976</v>
-      </c>
-      <c r="D1218" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1218" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr"/>
+      <c r="D1218" t="inlineStr"/>
+      <c r="E1218" t="inlineStr"/>
       <c r="F1218" t="b">
         <v>0</v>
       </c>
       <c r="G1218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1218" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38705,27 +38735,21 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1219" t="n">
-        <v>22.2478853726107</v>
-      </c>
-      <c r="D1219" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1219" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr"/>
+      <c r="D1219" t="inlineStr"/>
+      <c r="E1219" t="inlineStr"/>
       <c r="F1219" t="b">
         <v>0</v>
       </c>
       <c r="G1219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1219" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38737,21 +38761,27 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1220" t="inlineStr"/>
-      <c r="D1220" t="inlineStr"/>
-      <c r="E1220" t="inlineStr"/>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1220" t="n">
+        <v>56.4593704261673</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>2</v>
+      </c>
       <c r="F1220" t="b">
         <v>0</v>
       </c>
       <c r="G1220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1220" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -38763,17 +38793,17 @@
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1221" t="n">
-        <v>74.5889079825143</v>
+        <v>32.0669850496152</v>
       </c>
       <c r="D1221" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E1221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1221" t="b">
         <v>0</v>
@@ -38795,27 +38825,21 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1222" t="n">
-        <v>98.52583771001591</v>
-      </c>
-      <c r="D1222" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1222" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr"/>
+      <c r="D1222" t="inlineStr"/>
+      <c r="E1222" t="inlineStr"/>
       <c r="F1222" t="b">
         <v>0</v>
       </c>
       <c r="G1222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1222" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38827,11 +38851,11 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1223" t="n">
-        <v>83.6737787798304</v>
+        <v>21.136342099364</v>
       </c>
       <c r="D1223" t="n">
         <v>2024</v>
@@ -38859,11 +38883,11 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1224" t="n">
-        <v>51.4758878672647</v>
+        <v>28.4196149643503</v>
       </c>
       <c r="D1224" t="n">
         <v>2024</v>
@@ -38891,27 +38915,27 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1225" t="n">
-        <v>76.83115654306241</v>
+        <v>3.5396346488541</v>
       </c>
       <c r="D1225" t="n">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="E1225" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F1225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1225" t="b">
         <v>0</v>
       </c>
       <c r="H1225" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -38923,27 +38947,21 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1226" t="n">
-        <v>84.6596461582312</v>
-      </c>
-      <c r="D1226" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1226" t="n">
-        <v>2</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr"/>
+      <c r="D1226" t="inlineStr"/>
+      <c r="E1226" t="inlineStr"/>
       <c r="F1226" t="b">
         <v>0</v>
       </c>
       <c r="G1226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1226" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38955,27 +38973,21 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1227" t="n">
-        <v>90.9613941465855</v>
-      </c>
-      <c r="D1227" t="n">
-        <v>2010</v>
-      </c>
-      <c r="E1227" t="n">
-        <v>16</v>
-      </c>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr"/>
+      <c r="D1227" t="inlineStr"/>
+      <c r="E1227" t="inlineStr"/>
       <c r="F1227" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1227" t="b">
         <v>1</v>
       </c>
-      <c r="G1227" t="b">
-        <v>0</v>
-      </c>
       <c r="H1227" t="inlineStr">
         <is>
-          <t>stale_replaced_by_missing</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -38987,21 +38999,27 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>trade_openness</t>
-        </is>
-      </c>
-      <c r="C1228" t="inlineStr"/>
-      <c r="D1228" t="inlineStr"/>
-      <c r="E1228" t="inlineStr"/>
+          <t>stock_market_cap_gdp</t>
+        </is>
+      </c>
+      <c r="C1228" t="n">
+        <v>44.0698749158292</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>25</v>
+      </c>
       <c r="F1228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1228" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1228" t="inlineStr">
         <is>
-          <t>missing_original</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -39013,27 +39031,27 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1229" t="n">
-        <v>52.4649167856379</v>
+        <v>1.38334712502502</v>
       </c>
       <c r="D1229" t="n">
-        <v>2024</v>
+        <v>1996</v>
       </c>
       <c r="E1229" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F1229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1229" t="b">
         <v>0</v>
       </c>
       <c r="H1229" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -39045,11 +39063,11 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1230" t="n">
-        <v>25.3786342507088</v>
+        <v>216.290842771421</v>
       </c>
       <c r="D1230" t="n">
         <v>2024</v>
@@ -39077,27 +39095,27 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>stock_market_cap_gdp</t>
         </is>
       </c>
       <c r="C1231" t="n">
-        <v>26.0811657596499</v>
+        <v>4.28404166217623</v>
       </c>
       <c r="D1231" t="n">
-        <v>2024</v>
+        <v>2002</v>
       </c>
       <c r="E1231" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F1231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1231" t="b">
         <v>0</v>
       </c>
       <c r="H1231" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -39109,17 +39127,17 @@
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1232" t="n">
-        <v>7.145</v>
+        <v>27.929760849367</v>
       </c>
       <c r="D1232" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1232" t="b">
         <v>0</v>
@@ -39141,17 +39159,17 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1233" t="n">
-        <v>9.207000000000001</v>
+        <v>79.2424586933455</v>
       </c>
       <c r="D1233" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1233" t="b">
         <v>0</v>
@@ -39173,17 +39191,17 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1234" t="n">
-        <v>8.856</v>
+        <v>108.972446521476</v>
       </c>
       <c r="D1234" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1234" t="b">
         <v>0</v>
@@ -39205,17 +39223,17 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1235" t="n">
-        <v>2.967</v>
+        <v>46.9778716148403</v>
       </c>
       <c r="D1235" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1235" t="b">
         <v>0</v>
@@ -39237,17 +39255,17 @@
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1236" t="n">
-        <v>5.97</v>
+        <v>35.5845239385389</v>
       </c>
       <c r="D1236" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1236" t="b">
         <v>0</v>
@@ -39269,27 +39287,21 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
-        </is>
-      </c>
-      <c r="C1237" t="n">
-        <v>6.524</v>
-      </c>
-      <c r="D1237" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E1237" t="n">
+          <t>trade_openness</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr"/>
+      <c r="D1237" t="inlineStr"/>
+      <c r="E1237" t="inlineStr"/>
+      <c r="F1237" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1237" t="b">
         <v>1</v>
       </c>
-      <c r="F1237" t="b">
-        <v>0</v>
-      </c>
-      <c r="G1237" t="b">
-        <v>0</v>
-      </c>
       <c r="H1237" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -39301,17 +39313,17 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1238" t="n">
-        <v>6.907</v>
+        <v>65.1499212653783</v>
       </c>
       <c r="D1238" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1238" t="b">
         <v>0</v>
@@ -39333,17 +39345,17 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1239" t="n">
-        <v>8.974</v>
+        <v>63.859857248066</v>
       </c>
       <c r="D1239" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1239" t="b">
         <v>0</v>
@@ -39365,17 +39377,17 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1240" t="n">
-        <v>8.289999999999999</v>
+        <v>37.0254687077888</v>
       </c>
       <c r="D1240" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1240" t="b">
         <v>0</v>
@@ -39397,17 +39409,17 @@
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1241" t="n">
-        <v>6.843</v>
+        <v>71.33101376876169</v>
       </c>
       <c r="D1241" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1241" t="b">
         <v>0</v>
@@ -39429,17 +39441,17 @@
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>1.746</v>
+        <v>124.863238865053</v>
       </c>
       <c r="D1242" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1242" t="b">
         <v>0</v>
@@ -39461,17 +39473,17 @@
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1243" t="n">
-        <v>5.092</v>
+        <v>51.7835143952326</v>
       </c>
       <c r="D1243" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1243" t="b">
         <v>0</v>
@@ -39493,17 +39505,17 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>3.308</v>
+        <v>57.2031395531255</v>
       </c>
       <c r="D1244" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1244" t="b">
         <v>0</v>
@@ -39525,17 +39537,17 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1245" t="n">
-        <v>10.376</v>
+        <v>69.9502612382631</v>
       </c>
       <c r="D1245" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1245" t="b">
         <v>0</v>
@@ -39557,17 +39569,17 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1246" t="n">
-        <v>2.604</v>
+        <v>47.344196760267</v>
       </c>
       <c r="D1246" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1246" t="b">
         <v>0</v>
@@ -39589,27 +39601,27 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1247" t="n">
-        <v>11.962</v>
+        <v>194.350757310172</v>
       </c>
       <c r="D1247" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="E1247" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1247" t="b">
         <v>1</v>
       </c>
-      <c r="F1247" t="b">
-        <v>0</v>
-      </c>
       <c r="G1247" t="b">
         <v>0</v>
       </c>
       <c r="H1247" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -39621,17 +39633,17 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1248" t="n">
-        <v>4.92</v>
+        <v>91.1101585856976</v>
       </c>
       <c r="D1248" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1248" t="b">
         <v>0</v>
@@ -39653,17 +39665,17 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1249" t="n">
-        <v>14.944</v>
+        <v>22.2478853726107</v>
       </c>
       <c r="D1249" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1249" t="b">
         <v>0</v>
@@ -39685,27 +39697,21 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
-        </is>
-      </c>
-      <c r="C1250" t="n">
-        <v>3.286</v>
-      </c>
-      <c r="D1250" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E1250" t="n">
+          <t>trade_openness</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr"/>
+      <c r="D1250" t="inlineStr"/>
+      <c r="E1250" t="inlineStr"/>
+      <c r="F1250" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1250" t="b">
         <v>1</v>
       </c>
-      <c r="F1250" t="b">
-        <v>0</v>
-      </c>
-      <c r="G1250" t="b">
-        <v>0</v>
-      </c>
       <c r="H1250" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -39717,17 +39723,17 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1251" t="n">
-        <v>2.673</v>
+        <v>74.5889079825143</v>
       </c>
       <c r="D1251" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1251" t="b">
         <v>0</v>
@@ -39749,17 +39755,17 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>5.04</v>
+        <v>98.52583771001591</v>
       </c>
       <c r="D1252" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1252" t="b">
         <v>0</v>
@@ -39781,17 +39787,17 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>8.359999999999999</v>
+        <v>83.6737787798304</v>
       </c>
       <c r="D1253" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1253" t="b">
         <v>0</v>
@@ -39813,17 +39819,17 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>5.117</v>
+        <v>51.4758878672647</v>
       </c>
       <c r="D1254" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1254" t="b">
         <v>0</v>
@@ -39845,17 +39851,17 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>4.803</v>
+        <v>76.83115654306241</v>
       </c>
       <c r="D1255" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1255" t="b">
         <v>0</v>
@@ -39877,17 +39883,17 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>3.303</v>
+        <v>84.6596461582312</v>
       </c>
       <c r="D1256" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1256" t="b">
         <v>0</v>
@@ -39909,27 +39915,27 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>7.834</v>
+        <v>90.9613941465855</v>
       </c>
       <c r="D1257" t="n">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="E1257" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1257" t="b">
         <v>1</v>
       </c>
-      <c r="F1257" t="b">
-        <v>0</v>
-      </c>
       <c r="G1257" t="b">
         <v>0</v>
       </c>
       <c r="H1257" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>stale_replaced_by_missing</t>
         </is>
       </c>
     </row>
@@ -39941,27 +39947,21 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
-        </is>
-      </c>
-      <c r="C1258" t="n">
-        <v>3.329</v>
-      </c>
-      <c r="D1258" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E1258" t="n">
+          <t>trade_openness</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr"/>
+      <c r="D1258" t="inlineStr"/>
+      <c r="E1258" t="inlineStr"/>
+      <c r="F1258" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1258" t="b">
         <v>1</v>
       </c>
-      <c r="F1258" t="b">
-        <v>0</v>
-      </c>
-      <c r="G1258" t="b">
-        <v>0</v>
-      </c>
       <c r="H1258" t="inlineStr">
         <is>
-          <t>fresh</t>
+          <t>missing_original</t>
         </is>
       </c>
     </row>
@@ -39973,17 +39973,17 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>7.516</v>
+        <v>52.4649167856379</v>
       </c>
       <c r="D1259" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1259" t="b">
         <v>0</v>
@@ -40005,17 +40005,17 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>4.198</v>
+        <v>25.3786342507088</v>
       </c>
       <c r="D1260" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1260" t="b">
         <v>0</v>
@@ -40037,17 +40037,17 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>5.307</v>
+        <v>26.0811657596499</v>
       </c>
       <c r="D1261" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E1261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1261" t="b">
         <v>0</v>
@@ -40069,17 +40069,17 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>92.2742315972952</v>
+        <v>7.145</v>
       </c>
       <c r="D1262" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1262" t="b">
         <v>0</v>
@@ -40101,17 +40101,17 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>81.3249262966481</v>
+        <v>9.207000000000001</v>
       </c>
       <c r="D1263" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1263" t="b">
         <v>0</v>
@@ -40133,17 +40133,17 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>41.7532107338224</v>
+        <v>8.856</v>
       </c>
       <c r="D1264" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1264" t="b">
         <v>0</v>
@@ -40165,17 +40165,17 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>71.2361453773988</v>
+        <v>2.967</v>
       </c>
       <c r="D1265" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1265" t="b">
         <v>0</v>
@@ -40197,17 +40197,17 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>87.8958549533146</v>
+        <v>5.97</v>
       </c>
       <c r="D1266" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1266" t="b">
         <v>0</v>
@@ -40229,17 +40229,17 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>59.5397032429174</v>
+        <v>6.524</v>
       </c>
       <c r="D1267" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1267" t="b">
         <v>0</v>
@@ -40261,17 +40261,17 @@
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>82.70025657666331</v>
+        <v>6.907</v>
       </c>
       <c r="D1268" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1268" t="b">
         <v>0</v>
@@ -40293,17 +40293,17 @@
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>88.9950908479196</v>
+        <v>8.974</v>
       </c>
       <c r="D1269" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1269" t="b">
         <v>0</v>
@@ -40325,17 +40325,17 @@
       </c>
       <c r="B1270" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>78.5210811866115</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D1270" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1270" t="b">
         <v>0</v>
@@ -40357,17 +40357,17 @@
       </c>
       <c r="B1271" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>79.3107672397967</v>
+        <v>6.843</v>
       </c>
       <c r="D1271" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1271" t="b">
         <v>0</v>
@@ -40389,17 +40389,17 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>77.1664929228275</v>
+        <v>1.746</v>
       </c>
       <c r="D1272" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1272" t="b">
         <v>0</v>
@@ -40421,17 +40421,17 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>72.41218747521511</v>
+        <v>5.092</v>
       </c>
       <c r="D1273" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1273" t="b">
         <v>0</v>
@@ -40453,17 +40453,17 @@
       </c>
       <c r="B1274" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>63.2376932397602</v>
+        <v>3.308</v>
       </c>
       <c r="D1274" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1274" t="b">
         <v>0</v>
@@ -40485,17 +40485,17 @@
       </c>
       <c r="B1275" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>80.315199821207</v>
+        <v>10.376</v>
       </c>
       <c r="D1275" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1275" t="b">
         <v>0</v>
@@ -40517,17 +40517,17 @@
       </c>
       <c r="B1276" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>55.9547027274763</v>
+        <v>2.604</v>
       </c>
       <c r="D1276" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1276" t="b">
         <v>0</v>
@@ -40549,17 +40549,17 @@
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>26.477717988557</v>
+        <v>11.962</v>
       </c>
       <c r="D1277" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1277" t="b">
         <v>0</v>
@@ -40581,17 +40581,17 @@
       </c>
       <c r="B1278" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>58.7850728104829</v>
+        <v>4.92</v>
       </c>
       <c r="D1278" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1278" t="b">
         <v>0</v>
@@ -40613,17 +40613,17 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>55.0372652481002</v>
+        <v>14.944</v>
       </c>
       <c r="D1279" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1279" t="b">
         <v>0</v>
@@ -40645,17 +40645,17 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>58.9301585439922</v>
+        <v>3.286</v>
       </c>
       <c r="D1280" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1280" t="b">
         <v>0</v>
@@ -40677,17 +40677,17 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>79.7538805976118</v>
+        <v>2.673</v>
       </c>
       <c r="D1281" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1281" t="b">
         <v>0</v>
@@ -40709,17 +40709,17 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>59.2628402709961</v>
+        <v>5.04</v>
       </c>
       <c r="D1282" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1282" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1282" t="b">
         <v>0</v>
@@ -40741,17 +40741,17 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>65.99584476854881</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D1283" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1283" t="b">
         <v>0</v>
@@ -40773,17 +40773,17 @@
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>85.1912729600355</v>
+        <v>5.117</v>
       </c>
       <c r="D1284" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1284" t="b">
         <v>0</v>
@@ -40805,17 +40805,17 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>69.86225858869609</v>
+        <v>4.803</v>
       </c>
       <c r="D1285" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1285" t="b">
         <v>0</v>
@@ -40837,17 +40837,17 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>75.0674905102199</v>
+        <v>3.303</v>
       </c>
       <c r="D1286" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1286" t="b">
         <v>0</v>
@@ -40869,17 +40869,17 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>65.76418572008851</v>
+        <v>7.834</v>
       </c>
       <c r="D1287" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1287" t="b">
         <v>0</v>
@@ -40901,17 +40901,17 @@
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1288" t="n">
-        <v>53.961056681951</v>
+        <v>3.329</v>
       </c>
       <c r="D1288" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1288" t="b">
         <v>0</v>
@@ -40933,17 +40933,17 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1289" t="n">
-        <v>95.5981951588181</v>
+        <v>7.516</v>
       </c>
       <c r="D1289" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1289" t="b">
         <v>0</v>
@@ -40965,17 +40965,17 @@
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1290" t="n">
-        <v>80.1247798047184</v>
+        <v>4.198</v>
       </c>
       <c r="D1290" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1290" t="b">
         <v>0</v>
@@ -40997,17 +40997,17 @@
       </c>
       <c r="B1291" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="C1291" t="n">
-        <v>89.285859883201</v>
+        <v>5.307</v>
       </c>
       <c r="D1291" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E1291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1291" t="b">
         <v>0</v>
@@ -41029,11 +41029,11 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1292" t="n">
-        <v>0.385552</v>
+        <v>92.2742315972952</v>
       </c>
       <c r="D1292" t="n">
         <v>2024</v>
@@ -41061,11 +41061,11 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1293" t="n">
-        <v>0.5530661</v>
+        <v>81.3249262966481</v>
       </c>
       <c r="D1293" t="n">
         <v>2024</v>
@@ -41093,11 +41093,11 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1294" t="n">
-        <v>0.1039608</v>
+        <v>41.7532107338224</v>
       </c>
       <c r="D1294" t="n">
         <v>2024</v>
@@ -41125,11 +41125,11 @@
       </c>
       <c r="B1295" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1295" t="n">
-        <v>-0.4397641</v>
+        <v>71.2361453773988</v>
       </c>
       <c r="D1295" t="n">
         <v>2024</v>
@@ -41157,11 +41157,11 @@
       </c>
       <c r="B1296" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1296" t="n">
-        <v>0.3164771</v>
+        <v>87.8958549533146</v>
       </c>
       <c r="D1296" t="n">
         <v>2024</v>
@@ -41189,11 +41189,11 @@
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1297" t="n">
-        <v>0.99396</v>
+        <v>59.5397032429174</v>
       </c>
       <c r="D1297" t="n">
         <v>2024</v>
@@ -41221,11 +41221,11 @@
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1298" t="n">
-        <v>1.5036042</v>
+        <v>82.70025657666331</v>
       </c>
       <c r="D1298" t="n">
         <v>2024</v>
@@ -41253,11 +41253,11 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1299" t="n">
-        <v>0.994188</v>
+        <v>88.9950908479196</v>
       </c>
       <c r="D1299" t="n">
         <v>2024</v>
@@ -41285,11 +41285,11 @@
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1300" t="n">
-        <v>0.034564</v>
+        <v>78.5210811866115</v>
       </c>
       <c r="D1300" t="n">
         <v>2024</v>
@@ -41317,11 +41317,11 @@
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1301" t="n">
-        <v>1.0114744</v>
+        <v>79.3107672397967</v>
       </c>
       <c r="D1301" t="n">
         <v>2024</v>
@@ -41349,11 +41349,11 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1302" t="n">
-        <v>-1.26857129999999</v>
+        <v>77.1664929228275</v>
       </c>
       <c r="D1302" t="n">
         <v>2024</v>
@@ -41381,11 +41381,11 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1303" t="n">
-        <v>0.2011502</v>
+        <v>72.41218747521511</v>
       </c>
       <c r="D1303" t="n">
         <v>2024</v>
@@ -41413,11 +41413,11 @@
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1304" t="n">
-        <v>-0.1051406</v>
+        <v>63.2376932397602</v>
       </c>
       <c r="D1304" t="n">
         <v>2024</v>
@@ -41445,11 +41445,11 @@
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1305" t="n">
-        <v>1.1484423</v>
+        <v>80.315199821207</v>
       </c>
       <c r="D1305" t="n">
         <v>2024</v>
@@ -41477,11 +41477,11 @@
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1306" t="n">
-        <v>-0.4707611</v>
+        <v>55.9547027274763</v>
       </c>
       <c r="D1306" t="n">
         <v>2024</v>
@@ -41509,11 +41509,11 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1307" t="n">
-        <v>-0.1074386</v>
+        <v>26.477717988557</v>
       </c>
       <c r="D1307" t="n">
         <v>2024</v>
@@ -41541,11 +41541,11 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1308" t="n">
-        <v>-0.653545199999999</v>
+        <v>58.7850728104829</v>
       </c>
       <c r="D1308" t="n">
         <v>2024</v>
@@ -41573,11 +41573,11 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1309" t="n">
-        <v>-1.2648667</v>
+        <v>55.0372652481002</v>
       </c>
       <c r="D1309" t="n">
         <v>2024</v>
@@ -41605,11 +41605,11 @@
       </c>
       <c r="B1310" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1310" t="n">
-        <v>0.485209</v>
+        <v>58.9301585439922</v>
       </c>
       <c r="D1310" t="n">
         <v>2024</v>
@@ -41637,11 +41637,11 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1311" t="n">
-        <v>-0.338295</v>
+        <v>79.7538805976118</v>
       </c>
       <c r="D1311" t="n">
         <v>2024</v>
@@ -41669,11 +41669,11 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1312" t="n">
-        <v>-1.71577699999999</v>
+        <v>59.2628402709961</v>
       </c>
       <c r="D1312" t="n">
         <v>2024</v>
@@ -41701,11 +41701,11 @@
       </c>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1313" t="n">
-        <v>0.4411062</v>
+        <v>65.99584476854881</v>
       </c>
       <c r="D1313" t="n">
         <v>2024</v>
@@ -41733,11 +41733,11 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1314" t="n">
-        <v>0.0455746</v>
+        <v>85.1912729600355</v>
       </c>
       <c r="D1314" t="n">
         <v>2024</v>
@@ -41765,11 +41765,11 @@
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1315" t="n">
-        <v>-0.1497783</v>
+        <v>69.86225858869609</v>
       </c>
       <c r="D1315" t="n">
         <v>2024</v>
@@ -41797,11 +41797,11 @@
       </c>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1316" t="n">
-        <v>-0.7884205</v>
+        <v>75.0674905102199</v>
       </c>
       <c r="D1316" t="n">
         <v>2024</v>
@@ -41829,11 +41829,11 @@
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1317" t="n">
-        <v>0.0554088</v>
+        <v>65.76418572008851</v>
       </c>
       <c r="D1317" t="n">
         <v>2024</v>
@@ -41861,11 +41861,11 @@
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1318" t="n">
-        <v>0.4063023</v>
+        <v>53.961056681951</v>
       </c>
       <c r="D1318" t="n">
         <v>2024</v>
@@ -41893,11 +41893,11 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1319" t="n">
-        <v>1.2278086</v>
+        <v>95.5981951588181</v>
       </c>
       <c r="D1319" t="n">
         <v>2024</v>
@@ -41925,11 +41925,11 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1320" t="n">
-        <v>0.8869557</v>
+        <v>80.1247798047184</v>
       </c>
       <c r="D1320" t="n">
         <v>2024</v>
@@ -41957,11 +41957,11 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="C1321" t="n">
-        <v>-1.8174487</v>
+        <v>89.285859883201</v>
       </c>
       <c r="D1321" t="n">
         <v>2024</v>
@@ -41989,17 +41989,17 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1322" t="n">
-        <v>6.45</v>
+        <v>0.385552</v>
       </c>
       <c r="D1322" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1322" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1322" t="b">
         <v>0</v>
@@ -42021,17 +42021,17 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1323" t="n">
-        <v>16.34</v>
+        <v>0.5530661</v>
       </c>
       <c r="D1323" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1323" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1323" t="b">
         <v>0</v>
@@ -42053,17 +42053,17 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1324" t="n">
-        <v>18.05</v>
+        <v>0.1039608</v>
       </c>
       <c r="D1324" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1324" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1324" t="b">
         <v>0</v>
@@ -42085,17 +42085,17 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1325" t="n">
-        <v>5.08</v>
+        <v>-0.4397641</v>
       </c>
       <c r="D1325" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1325" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1325" t="b">
         <v>0</v>
@@ -42117,17 +42117,17 @@
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>7.26</v>
+        <v>0.3164771</v>
       </c>
       <c r="D1326" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1326" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1326" t="b">
         <v>0</v>
@@ -42149,17 +42149,17 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>14.58</v>
+        <v>0.99396</v>
       </c>
       <c r="D1327" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1327" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1327" t="b">
         <v>0</v>
@@ -42181,17 +42181,17 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>1.37</v>
+        <v>1.5036042</v>
       </c>
       <c r="D1328" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1328" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1328" t="b">
         <v>0</v>
@@ -42213,17 +42213,17 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>0.46</v>
+        <v>0.994188</v>
       </c>
       <c r="D1329" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1329" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1329" t="b">
         <v>0</v>
@@ -42245,17 +42245,17 @@
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>2.83</v>
+        <v>0.034564</v>
       </c>
       <c r="D1330" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1330" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1330" t="b">
         <v>0</v>
@@ -42277,17 +42277,17 @@
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>1.3</v>
+        <v>1.0114744</v>
       </c>
       <c r="D1331" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1331" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1331" t="b">
         <v>0</v>
@@ -42309,17 +42309,17 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>9.16</v>
+        <v>-1.26857129999999</v>
       </c>
       <c r="D1332" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1332" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1332" t="b">
         <v>0</v>
@@ -42341,17 +42341,17 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>3.97</v>
+        <v>0.2011502</v>
       </c>
       <c r="D1333" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1333" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1333" t="b">
         <v>0</v>
@@ -42373,17 +42373,17 @@
       </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>5.19</v>
+        <v>-0.1051406</v>
       </c>
       <c r="D1334" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1334" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1334" t="b">
         <v>0</v>
@@ -42405,17 +42405,17 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>1.33</v>
+        <v>1.1484423</v>
       </c>
       <c r="D1335" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1335" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1335" t="b">
         <v>0</v>
@@ -42437,17 +42437,17 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>2.39</v>
+        <v>-0.4707611</v>
       </c>
       <c r="D1336" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1336" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1336" t="b">
         <v>0</v>
@@ -42469,17 +42469,17 @@
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>9.27</v>
+        <v>-0.1074386</v>
       </c>
       <c r="D1337" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1337" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1337" t="b">
         <v>0</v>
@@ -42501,17 +42501,17 @@
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>2.11</v>
+        <v>-0.653545199999999</v>
       </c>
       <c r="D1338" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1338" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1338" t="b">
         <v>0</v>
@@ -42533,17 +42533,17 @@
       </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>6.76</v>
+        <v>-1.2648667</v>
       </c>
       <c r="D1339" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E1339" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F1339" t="b">
         <v>0</v>
@@ -42565,17 +42565,17 @@
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>9.24</v>
+        <v>0.485209</v>
       </c>
       <c r="D1340" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1340" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1340" t="b">
         <v>0</v>
@@ -42597,17 +42597,17 @@
       </c>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>1.62</v>
+        <v>-0.338295</v>
       </c>
       <c r="D1341" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1341" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1341" t="b">
         <v>0</v>
@@ -42629,17 +42629,17 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>2.04</v>
+        <v>-1.71577699999999</v>
       </c>
       <c r="D1342" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1342" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1342" t="b">
         <v>0</v>
@@ -42661,17 +42661,17 @@
       </c>
       <c r="B1343" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>5.93</v>
+        <v>0.4411062</v>
       </c>
       <c r="D1343" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1343" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1343" t="b">
         <v>0</v>
@@ -42693,17 +42693,17 @@
       </c>
       <c r="B1344" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>0.66</v>
+        <v>0.0455746</v>
       </c>
       <c r="D1344" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1344" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1344" t="b">
         <v>0</v>
@@ -42725,17 +42725,17 @@
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>4.63</v>
+        <v>-0.1497783</v>
       </c>
       <c r="D1345" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1345" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1345" t="b">
         <v>0</v>
@@ -42757,17 +42757,17 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>2.16</v>
+        <v>-0.7884205</v>
       </c>
       <c r="D1346" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1346" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1346" t="b">
         <v>0</v>
@@ -42789,17 +42789,17 @@
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>7.8</v>
+        <v>0.0554088</v>
       </c>
       <c r="D1347" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1347" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1347" t="b">
         <v>0</v>
@@ -42821,17 +42821,17 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>7.51</v>
+        <v>0.4063023</v>
       </c>
       <c r="D1348" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1348" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1348" t="b">
         <v>0</v>
@@ -42853,17 +42853,17 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>4.85</v>
+        <v>1.2278086</v>
       </c>
       <c r="D1349" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1349" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1349" t="b">
         <v>0</v>
@@ -42885,17 +42885,17 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>weighted_mean_applied_tariff_all_products</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>1.49</v>
+        <v>0.8869557</v>
       </c>
       <c r="D1350" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E1350" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1350" t="b">
         <v>0</v>
@@ -42917,25 +42917,985 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
+          <t>voice_accountability</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>-1.8174487</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1351" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1351" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
           <t>weighted_mean_applied_tariff_all_products</t>
         </is>
       </c>
-      <c r="C1351" t="n">
+      <c r="C1352" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1352" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1352" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>BHS</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1353" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1353" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>BLZ</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1354" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1354" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1355" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1355" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1355" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1356" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1356" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>BRB</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1357" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1357" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1358" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1358" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1359" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1359" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1360" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1360" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1361" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1361" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1362" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1362" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1363" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1363" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>ECU</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1364" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1364" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1365" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1365" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1366" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1366" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>GUY</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1367" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1367" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1368" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1368" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>HTI</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1369" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1369" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>JAM</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1370" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1370" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1371" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1371" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>NIC</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1372" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1372" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>PAN</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1373" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1373" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1374" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1374" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1375" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1375" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1376" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1376" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>SUR</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1377" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1377" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>TTO</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1378" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1378" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1379" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1379" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1380" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1380" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>weighted_mean_applied_tariff_all_products</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
         <v>12.84</v>
       </c>
-      <c r="D1351" t="n">
+      <c r="D1381" t="n">
         <v>2022</v>
       </c>
-      <c r="E1351" t="n">
+      <c r="E1381" t="n">
         <v>4</v>
       </c>
-      <c r="F1351" t="b">
-        <v>0</v>
-      </c>
-      <c r="G1351" t="b">
-        <v>0</v>
-      </c>
-      <c r="H1351" t="inlineStr">
+      <c r="F1381" t="b">
+        <v>0</v>
+      </c>
+      <c r="G1381" t="b">
+        <v>0</v>
+      </c>
+      <c r="H1381" t="inlineStr">
         <is>
           <t>fresh</t>
         </is>
@@ -42952,7 +43912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43123,7 +44083,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>interest_rate_spread</t>
+          <t>financial_system_deposits_gdp</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -43156,7 +44116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>financial_system_deposits_gdp</t>
+          <t>interest_rate_spread</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -43222,7 +44182,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>personal_remittances_gdp</t>
+          <t>digital_payment_adults_pct</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -43233,7 +44193,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>financial</t>
+          <t>digital_tech</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -43243,7 +44203,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>triennial</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -43255,7 +44215,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>trade_openness</t>
+          <t>personal_remittances_gdp</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -43266,7 +44226,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -43274,7 +44234,11 @@
           <t>world_bank</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Mantener con documentación</t>
@@ -43284,7 +44248,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>current_account_gdp</t>
+          <t>domestic_credit_private_gdp</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -43295,7 +44259,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -43303,7 +44267,11 @@
           <t>world_bank</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Mantener con documentación</t>
@@ -43313,7 +44281,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>digital_payment_adults_pct</t>
+          <t>ict_goods_exports_pct_total_goods_exports</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -43334,7 +44302,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>triennial</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -43346,7 +44314,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>domestic_credit_private_gdp</t>
+          <t>current_account_gdp</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -43357,7 +44325,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>financial</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -43365,11 +44333,7 @@
           <t>world_bank</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Mantener con documentación</t>
@@ -43379,7 +44343,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ict_goods_exports_pct_total_goods_exports</t>
+          <t>trade_openness</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -43390,7 +44354,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>digital_tech</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -43398,11 +44362,7 @@
           <t>world_bank</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Mantener con documentación</t>
@@ -43412,7 +44372,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>account_ownership</t>
+          <t>return_on_equity</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -43433,7 +44393,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>triennial</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -43445,7 +44405,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gdp_per_capita_ppp</t>
+          <t>commercial_bank_branches_per_100k_adults</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -43456,7 +44416,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>digital_tech</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -43478,7 +44438,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inflation_rate</t>
+          <t>gdp_per_capita_ppp</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -43511,7 +44471,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>commercial_bank_branches_per_100k_adults</t>
+          <t>account_ownership</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -43522,7 +44482,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>digital_tech</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -43532,7 +44492,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>triennial</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -43544,18 +44504,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>regulatory_quality</t>
+          <t>inflation_rate</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>institutional</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -43570,7 +44530,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mantener</t>
+          <t>Mantener con documentación</t>
         </is>
       </c>
     </row>
@@ -43610,7 +44570,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>unemployment_rate</t>
+          <t>regulatory_quality</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -43621,7 +44581,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>institutional</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -43629,7 +44589,11 @@
           <t>world_bank</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Mantener</t>
@@ -43705,7 +44669,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>urban_population_pct</t>
+          <t>secure_internet_servers_per_million</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -43716,7 +44680,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>digital_tech</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -43738,7 +44702,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mobile_subscriptions</t>
+          <t>urban_population_pct</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -43749,7 +44713,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>digital_tech</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -43771,7 +44735,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>internet_users_pct</t>
+          <t>mobile_subscriptions</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -43804,7 +44768,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>voice_accountability</t>
+          <t>internet_users_pct</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -43815,7 +44779,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>institutional</t>
+          <t>digital_tech</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -43837,7 +44801,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>secure_internet_servers_per_million</t>
+          <t>voice_accountability</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -43848,7 +44812,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>digital_tech</t>
+          <t>institutional</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -43870,7 +44834,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hofstede_ivr</t>
+          <t>unemployment_rate</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -43881,19 +44845,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>proximity</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>complementary</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>static</t>
-        </is>
-      </c>
+          <t>world_bank</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Mantener</t>
@@ -43903,7 +44863,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hofstede_uai</t>
+          <t>hofstede_lto</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -43936,7 +44896,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gdp_growth</t>
+          <t>hofstede_uai</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -43947,17 +44907,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>proximity</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>world_bank</t>
+          <t>complementary</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>static</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -43969,7 +44929,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bank_npl_ratio</t>
+          <t>gdp_growth</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -43980,7 +44940,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>financial</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -44002,7 +44962,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>colombian_diaspora_stock</t>
+          <t>bank_npl_ratio</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -44013,12 +44973,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>proximity</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>complementary</t>
+          <t>world_bank</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -44035,7 +44995,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>common_language_spanish</t>
+          <t>colombian_diaspora_stock</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -44056,7 +45016,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -44068,7 +45028,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>control_of_corruption</t>
+          <t>common_language_spanish</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -44079,17 +45039,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>institutional</t>
+          <t>proximity</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>world_bank</t>
+          <t>complementary</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>static</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -44101,7 +45061,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>country_risk_premium</t>
+          <t>control_of_corruption</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -44117,7 +45077,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>damodaran_country_risk_premium</t>
+          <t>world_bank</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -44134,7 +45094,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fdi_net_inflows_gdp</t>
+          <t>country_risk_premium</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -44145,15 +45105,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>macro</t>
+          <t>institutional</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>world_bank</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>damodaran_country_risk_premium</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Mantener</t>
@@ -44163,7 +45127,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gdp_nominal</t>
+          <t>fdi_net_inflows_gdp</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -44182,11 +45146,7 @@
           <t>world_bank</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Mantener</t>
@@ -44196,7 +45156,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hofstede_pdi</t>
+          <t>gdp_nominal</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -44207,17 +45167,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>proximity</t>
+          <t>macro</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>complementary</t>
+          <t>world_bank</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -44229,7 +45189,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>geographic_distance_km</t>
+          <t>hofstede_pdi</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -44262,7 +45222,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>government_effectiveness</t>
+          <t>geographic_distance_km</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -44273,17 +45233,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>institutional</t>
+          <t>proximity</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>world_bank</t>
+          <t>complementary</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>static</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -44295,7 +45255,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>heritage_efi</t>
+          <t>government_effectiveness</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -44311,7 +45271,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>complementary</t>
+          <t>world_bank</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -44328,7 +45288,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hofstede_idv</t>
+          <t>heritage_efi</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -44339,7 +45299,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>proximity</t>
+          <t>institutional</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -44349,7 +45309,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>static</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -44361,7 +45321,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hofstede_lto</t>
+          <t>hofstede_idv</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -44394,7 +45354,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hofstede_mas</t>
+          <t>hofstede_ivr</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -44427,27 +45387,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>hofstede_mas</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>proximity</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>complementary</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Mantener</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>weighted_mean_applied_tariff_all_products</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>macro</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>world_bank</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>Mantener</t>
         </is>
@@ -44504,13 +45497,13 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="D2" t="n">
         <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5217391304347826</v>
       </c>
     </row>
     <row r="3">
@@ -44523,13 +45516,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3260869565217391</v>
       </c>
     </row>
     <row r="4">
@@ -44542,13 +45535,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3260869565217391</v>
       </c>
     </row>
     <row r="5">
@@ -44561,13 +45554,13 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="6">
@@ -44580,70 +45573,70 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2391304347826087</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04444444444444445</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2391304347826087</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="10">
@@ -44656,32 +45649,32 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.1956521739130435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.108695652173913</v>
       </c>
     </row>
     <row r="12">
@@ -44694,146 +45687,146 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.108695652173913</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.108695652173913</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02222222222222222</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
     </row>
     <row r="20">
@@ -44846,13 +45839,13 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
     </row>
     <row r="21">
@@ -44871,7 +45864,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="22">
@@ -44890,7 +45883,7 @@
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="23">
@@ -44903,13 +45896,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="24">
@@ -44922,13 +45915,13 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="25">
@@ -44941,13 +45934,13 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="26">
@@ -44960,13 +45953,13 @@
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="27">
@@ -44979,13 +45972,13 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
     </row>
     <row r="28">
@@ -45107,10 +46100,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -45123,10 +46116,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -45139,10 +46132,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -45155,10 +46148,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -45171,10 +46164,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -45187,10 +46180,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2444444444444444</v>
+        <v>0.2391304347826087</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -45199,14 +46192,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2391304347826087</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -45215,14 +46208,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -45235,10 +46228,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.8043478260869565</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -45251,10 +46244,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8913043478260869</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -45267,10 +46260,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8913043478260869</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -45283,10 +46276,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8913043478260869</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
@@ -45299,10 +46292,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -45315,10 +46308,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -45331,10 +46324,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -45347,10 +46340,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -45363,10 +46356,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -45379,10 +46372,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -45395,10 +46388,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -45411,10 +46404,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -45427,10 +46420,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -45443,10 +46436,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -45459,10 +46452,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -45475,10 +46468,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D25" t="b">
         <v>0</v>
@@ -45491,10 +46484,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -45507,10 +46500,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9777777777777777</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
